--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2606-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2606-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F149BEDB-B1C4-4565-A62D-4E9F838E02F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4D85EBA-97F5-4AF7-934F-5B1F9415F41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{08A779FA-8F23-4DA2-A852-831764745EE2}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{5FE9B693-D11F-4987-90F6-ACCAFF3153BA}"/>
   </bookViews>
   <sheets>
     <sheet name="2606-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1403,22 +1403,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E35ECE-5C3B-4C9F-AA7F-8B78E42EB06A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D5A3E1F-3A30-4229-B732-16F9E84136AE}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="5" width="7.33203125" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="5" width="9" customWidth="1"/>
+    <col min="6" max="7" width="9.5" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1446,7 +1446,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1476,7 +1476,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1572,7 +1572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="37">
         <v>2024</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>2023</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>2021</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>2019</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>2017</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="35">
         <v>2015</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="35">
         <v>2013</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="35">
         <v>2011</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>7.72</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="35">
         <v>2009</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>8.61</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="35">
         <v>2007</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2006</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="35">
         <v>2005</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2004</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>7.59</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="35">
         <v>2003</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2002</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="35">
         <v>2001</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>9.64</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>1999</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="35">
         <v>1997</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>1996</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="35">
         <v>1995</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>1994</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="35">
         <v>1993</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>1992</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="35">
         <v>1991</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>1990</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="35">
         <v>1989</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>1988</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="35">
         <v>1987</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>1984</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="35" t="s">
         <v>25</v>
       </c>
